--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_780_Trinidad_Tobago.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_780_Trinidad_Tobago.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R79fbe1b0729b4a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R361f976598794741"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R40258da8e5ae4194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R76bd01e22b704681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re0310792ba8648e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R97118eecc2e34dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R7e704a41e6444a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rcc8f887560294f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R130bf614011b42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R50e6fa64e1094e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R713f819d06334ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R353d5923bd394806"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ780CommercialTable" displayName="EEZ780CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ780CommercialTable" displayName="EEZ780CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ780FunctionalTable" displayName="EEZ780FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ780FunctionalTable" displayName="EEZ780FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ780ValidationTable" displayName="EEZ780ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ780ValidationTable" displayName="EEZ780ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7193,7 +7147,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R717e4a5e236a4891"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa2adffc2020441b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7203,20 +7157,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7224,498 +7168,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>59.733761025999996</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>59.733761025999996</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$98,A2,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>9467.163121020641</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>9467.163121020641</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>737.1221390302001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.2732800778506586</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>187.6204087796714</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>737.1221390302001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>206.87752201738084</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$98,A3,'Species'!$U$2:$U$98))</x:f>
-        <x:v>152494.00154671908</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.2732800778506586</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>187.6204087796714</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>138299.1570453919</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>14194.84450132717</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1026386914033626</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10263869140336267</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>10.7176327978</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.426447592291852</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>266.96085974590255</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>10.7176327978</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>291.54343079220956</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$98,A4,'Species'!$U$2:$U$98))</x:f>
-        <x:v>3124.6554358417197</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.426447592291852</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>266.96085974590255</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2861.188466141571</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>263.46696970014864</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.092083053185044</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.09208305318504396</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>551.8367535574</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>551.8367535574</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$98,A5,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>79764.67905511854</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>79764.67905511854</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3934.6822410002</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3312687671748042</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>214.42171593105155</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3934.6822410002</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>294.0833545822502</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$98,A6,'Species'!$U$2:$U$98))</x:f>
-        <x:v>1157124.5526485445</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3312687671748042</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>214.42171593105155</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>843681.3177586982</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>313443.2348898463</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3715185204320175</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3715185204320174</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>12489.012441006602</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.9885544952973584</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>973.9899939833358</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>12489.012441006602</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1237.1161706318253</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$98,A7,'Species'!$U$2:$U$98))</x:f>
-        <x:v>15450359.245991312</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.9885544952973584</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>973.9899939833358</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>12164173.152273826</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3286186.0937174857</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2701528540066207</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.27015285400662065</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1319.0404729799998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.255937114907915</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1802.756685900413</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1319.0404729799998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1823.8914783924563</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$98,A8,'Species'!$U$2:$U$98))</x:f>
-        <x:v>2405786.6783229765</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.255937114907915</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1802.756685900413</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2377909.0316379378</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>27877.646685038693</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.01172359678782</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.01172359678782</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>421.0731178676</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.4206888265471775</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2634.4431221001246</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>421.0731178676</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2668.9215197345866</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$98,A9,'Species'!$U$2:$U$98))</x:f>
-        <x:v>1123811.1056585757</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.4206888265471775</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2634.4431221001246</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1109293.1792675538</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>14517.926391021814</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0130875467931821</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.013087546793182067</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R432681b1f3264e2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd60352e52c35424f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7725,20 +7345,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7746,1146 +7356,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10.3424559853</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8110923904458534</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>647.2803014836986</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10.3424559853</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>647.4587852942344</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$98,A2,'Species'!$U$2:$U$98))</x:f>
-        <x:v>6696.313989201422</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8110923904458534</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>647.2803014836986</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6694.468028246868</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1.8459609545543572</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0002757442334127</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00027574423341263955</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.0590367644</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.6700000000000004</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>467.7351412871986</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.0590367644</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>467.7351412871982</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$98,A3,'Species'!$U$2:$U$98))</x:f>
-        <x:v>27.61356933777303</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.6700000000000004</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>467.7351412871986</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>27.613569337773054</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>-2.4868995751603507e-14</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>-9.00607793487414e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.2383843769</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.2383843769</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$98,A4,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2709.289815480498</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>2709.289815480498</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>174.33026678829998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.149999430657213</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1412.535692843447</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>174.33026678829998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1412.538568718286</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$98,A5,'Species'!$U$2:$U$98))</x:f>
-        <x:v>246248.22553342217</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.149999430657213</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1412.535692843447</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>246247.72418139424</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0.5013520279317163</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000020359661377</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0000020359661377516074</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.0053589353</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.89</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>776.247116628692</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.0053589353</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>776.247116628692</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$98,A6,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4.159858074824714</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.89</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>776.247116628692</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>4.159858074824714</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2002.2772957</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.917547933303992</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>827.0807888600082</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2002.2772957</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1548.049719602306</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$98,A7,'Species'!$U$2:$U$98))</x:f>
-        <x:v>3099624.806174448</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.917547933303992</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>827.0807888600082</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1656045.0852440398</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1443579.7209304085</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.8717031521624776</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8717031521624776</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2.9927225967</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.439153546032367</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>274.88658505517225</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2.9927225967</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>288.1520138073741</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$98,A8,'Species'!$U$2:$U$98))</x:f>
-        <x:v>862.3590430059389</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.439153546032367</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>274.88658505517225</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>822.6592946243105</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>39.69974838162841</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0482578251300965</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.048257825130096375</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>100.3690182655</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8464951007272834</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>702.2554215530593</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>100.3690182655</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>727.3458670187639</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$98,A9,'Species'!$U$2:$U$98))</x:f>
-        <x:v>73002.99061214225</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8464951007272834</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>702.2554215530593</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>70484.6872329054</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2518.3033792368515</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0357283755961848</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.03572837559618474</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1316.0477503833</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.2577944993702</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1810.4832005971302</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1316.0477503833</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1827.3837849572974</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$98,A10,'Species'!$U$2:$U$98))</x:f>
-        <x:v>2404924.319279971</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.2577944993702</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1810.4832005971302</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2382682.34325261</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>22241.976027361117</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.009334847379193</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.009334847379193023</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>174.2302191255</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.164253119228004</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>145.96647467114704</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>174.2302191255</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>218.8404058701445</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$98,A11,'Species'!$U$2:$U$98))</x:f>
-        <x:v>38128.611868268636</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.164253119228004</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>145.96647467114704</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>25431.770866930696</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>12696.84100133794</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.499251155877935</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.4992511558779349</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>12.6233422199</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3100000000000005</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>204.17379446695315</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>12.6233422199</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$98,A12,'Species'!$U$2:$U$98))</x:f>
-        <x:v>2577.355679891872</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3100000000000005</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>204.17379446695315</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2577.355679891875</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>-2.7284841053187847e-12</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>-1.058637007924824e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>5987.9251397284</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.476286955777393</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>299.4242399151118</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>5987.9251397284</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>342.9076545177088</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$98,A13,'Species'!$U$2:$U$98))</x:f>
-        <x:v>2053305.3650918892</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.476286955777393</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>299.4242399151118</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1792929.9336317657</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>260375.4314601235</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.145223428186458</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.14522342818645792</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>5434.008097151701</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.171056100839918</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1482.7096046916167</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>5434.008097151701</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1601.710113168</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$98,A14,'Species'!$U$2:$U$98))</x:f>
-        <x:v>8703705.724244678</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.171056100839918</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1482.7096046916167</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>8057055.997618843</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>646649.7266258355</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.080258810019062</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0802588100190621</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>2907.4176766909</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.9983178871328677</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>996.1342831827886</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>2907.4176766909</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1209.4935789414778</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$98,A15,'Species'!$U$2:$U$98))</x:f>
-        <x:v>3516503.011258593</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.9983178871328677</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>996.1342831827886</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2896178.423283458</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>620324.5879751346</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2141872831411609</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.21418728314116076</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>50.514647109500004</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>26.915348039269166</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>50.514647109500004</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>26.915348039269166</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$98,A16,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1359.6193080330547</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.43</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>26.915348039269166</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>1359.6193080330547</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>562.8919199047</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3070268598165966</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>202.78081295194733</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>562.8919199047</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>203.17468706570344</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$98,A17,'Species'!$U$2:$U$98))</x:f>
-        <x:v>114365.38967845043</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3070268598165966</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>202.78081295194733</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>114143.68112235748</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>221.7085560929554</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0019423638164893</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0019423638164892602</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>138.3279808818</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.074111277668059</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>118.60726122330706</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>138.3279808818</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>130.30791792303228</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$98,A18,'Species'!$U$2:$U$98))</x:f>
-        <x:v>18025.23117920437</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.074111277668059</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>118.60726122330706</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>16406.702962940275</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1618.5282162640942</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.098650424763589</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.09865042476358911</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>611.5705145834</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.1639069091528516</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>145.85015975374137</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>611.5705145834</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>145.9060566988316</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$98,A19,'Species'!$U$2:$U$98))</x:f>
-        <x:v>89231.84217613918</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.1639069091528516</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>145.85015975374137</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>89197.65725266672</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>34.184923472465016</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0003832491180304</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.00038324911803042897</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>25.3290992765</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.4581124370536402</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>287.1523911518452</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>25.3290992765</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>296.3073381372859</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$98,A20,'Species'!$U$2:$U$98))</x:f>
-        <x:v>7505.1979840347685</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.4581124370536402</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>287.1523911518452</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>7273.311422969447</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>231.88656106532108</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0318818413759945</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.03188184137599454</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>10.7176327978</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.426447592291852</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>266.96085974590255</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>10.7176327978</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>291.54343079220956</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$98,A21,'Species'!$U$2:$U$98))</x:f>
-        <x:v>3124.6554358417197</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.426447592291852</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>266.96085974590255</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>2861.188466141571</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>263.46696970014864</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.092083053185044</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.09208305318504396</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R540b98219e0e4ffe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d0e2613a5364b35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9060,7 +7926,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9159,7 +8025,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>20381932.08178011</x:v>
+        <x:v>16725448.86862569</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9173,7 +8039,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>20381932.08178011</x:v>
+        <x:v>17371133.672092713</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9187,7 +8053,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-3656483.2131544165</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9201,7 +8067,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-3010798.4096873924</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9212,9 +8078,9 @@
         <x:v>EEZ_780</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9226,47 +8092,19 @@
         <x:v>EEZ_780</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_780</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_780</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45dd73375f3e42d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra70cb24b327f4054"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9313,7 +8151,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
